--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.31085325982435</v>
+      </c>
+      <c r="C2">
         <v>28.22103981024425</v>
-      </c>
-      <c r="C2">
-        <v>29.31085325982435</v>
       </c>
       <c r="D2">
         <v>3.543455544954795</v>
       </c>
       <c r="E2">
-        <v>17.91449290696444</v>
+        <v>18.60629786679906</v>
       </c>
       <c r="F2">
         <v>63.47920922623651</v>
       </c>
       <c r="G2">
-        <v>18.60629786679906</v>
+        <v>17.91449290696444</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>38.84057971014493</v>
+      </c>
+      <c r="C3">
         <v>52.17391304347826</v>
-      </c>
-      <c r="C3">
-        <v>38.84057971014493</v>
       </c>
       <c r="D3">
         <v>1.916666666666667</v>
       </c>
       <c r="E3">
-        <v>27.31411229135053</v>
+        <v>20.33383915022762</v>
       </c>
       <c r="F3">
         <v>52.35204855842185</v>
       </c>
       <c r="G3">
-        <v>20.33383915022762</v>
+        <v>27.31411229135053</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.21649484536083</v>
+      </c>
+      <c r="C4">
         <v>37.11340206185567</v>
-      </c>
-      <c r="C4">
-        <v>32.21649484536083</v>
       </c>
       <c r="D4">
         <v>2.694444444444445</v>
       </c>
       <c r="E4">
-        <v>21.91780821917808</v>
+        <v>19.02587519025875</v>
       </c>
       <c r="F4">
         <v>59.05631659056316</v>
       </c>
       <c r="G4">
-        <v>19.02587519025875</v>
+        <v>21.91780821917808</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.61538461538461</v>
+      </c>
+      <c r="C5">
         <v>40.17094017094017</v>
-      </c>
-      <c r="C5">
-        <v>34.61538461538461</v>
       </c>
       <c r="D5">
         <v>2.48936170212766</v>
       </c>
       <c r="E5">
+        <v>19.80440097799511</v>
+      </c>
+      <c r="F5">
+        <v>57.21271393643033</v>
+      </c>
+      <c r="G5">
         <v>22.98288508557457</v>
-      </c>
-      <c r="F5">
-        <v>57.21271393643031</v>
-      </c>
-      <c r="G5">
-        <v>19.80440097799511</v>
       </c>
     </row>
   </sheetData>
